--- a/app/content/touming.xlsx
+++ b/app/content/touming.xlsx
@@ -1595,7 +1595,7 @@
         <v>缓言</v>
       </c>
       <c r="C2" t="str">
-        <v>理</v>
+        <v>策</v>
       </c>
       <c r="D2" t="str">
         <v>把话说得滴水不漏。</v>
@@ -1618,7 +1618,7 @@
         <v>放狂</v>
       </c>
       <c r="C3" t="str">
-        <v>威</v>
+        <v>隐</v>
       </c>
       <c r="D3" t="str">
         <v>把胸中那口血气压出来。</v>
@@ -1641,7 +1641,7 @@
         <v>算账</v>
       </c>
       <c r="C4" t="str">
-        <v>利</v>
+        <v>器</v>
       </c>
       <c r="D4" t="str">
         <v>把兵马钱粮算给他们听。</v>
@@ -1664,7 +1664,7 @@
         <v>动情</v>
       </c>
       <c r="C5" t="str">
-        <v>情</v>
+        <v>策</v>
       </c>
       <c r="D5" t="str">
         <v>提兄弟，提家乡，提死人。</v>
@@ -1687,7 +1687,7 @@
         <v>结阵</v>
       </c>
       <c r="C6" t="str">
-        <v>理</v>
+        <v>器</v>
       </c>
       <c r="D6" t="str">
         <v>亲兵结环阵，枪锋向外。</v>
@@ -1710,7 +1710,7 @@
         <v>突围</v>
       </c>
       <c r="C7" t="str">
-        <v>威</v>
+        <v>器</v>
       </c>
       <c r="D7" t="str">
         <v>凿穿一点，纵马夺路。</v>
@@ -1733,7 +1733,7 @@
         <v>背靠背结阵</v>
       </c>
       <c r="C8" t="str">
-        <v>威</v>
+        <v>器</v>
       </c>
       <c r="D8" t="str">
         <v>残骑结成环阵，枪锋向外，滚着走。</v>
@@ -1756,7 +1756,7 @@
         <v>据守</v>
       </c>
       <c r="C9" t="str">
-        <v>利</v>
+        <v>势</v>
       </c>
       <c r="D9" t="str">
         <v>依托地形，且战且退。</v>
@@ -1779,7 +1779,7 @@
         <v>断后</v>
       </c>
       <c r="C10" t="str">
-        <v>情</v>
+        <v>隐</v>
       </c>
       <c r="D10" t="str">
         <v>让弟兄先走，我来挡箭。</v>
@@ -1873,7 +1873,7 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>理,威,理,情,威,理,情</v>
+        <v>策,势,策,策,势,策,策</v>
       </c>
       <c r="I2" t="str">
         <v>t_wen,t_kuang,t_li,t_qing</v>
@@ -1908,7 +1908,7 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>利,理,威,利,情,理,威</v>
+        <v>策,策,势,策,策,策,势</v>
       </c>
       <c r="I3" t="str">
         <v>t_wen,t_kuang,t_li,t_qing</v>
